--- a/list.xlsx
+++ b/list.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21781\Documents\WORK\CJUG\いまさらチーム\4_作業\成果物アンケート\files\成果物一覧Excel\FIX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kmbiologics365.sharepoint.com/sites/KMB--CJUGSDTM3.3/Shared Documents/CJUG SDTM：いまさら3.3/CJUG成果物アンケート/03_成果物一覧/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA65DDD0-FE00-4EE2-B75E-AB117CA86419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{6E3D1D72-4162-4EFF-98DB-631641C35543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B97D7F6A-F081-4943-A659-8BF29C232FDB}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="690" windowWidth="24660" windowHeight="14385" xr2:uid="{3688DF61-2926-4D30-83DE-4F7536F96066}"/>
+    <workbookView xWindow="0" yWindow="-15855" windowWidth="28905" windowHeight="13770" xr2:uid="{3688DF61-2926-4D30-83DE-4F7536F96066}"/>
   </bookViews>
   <sheets>
-    <sheet name="J3C_CJUG_SDTM_成果物一覧" sheetId="6" r:id="rId1"/>
+    <sheet name="J3C_CJUG_成果物一覧(2027.7)" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">J3C_CJUG_SDTM_成果物一覧!$A$1:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'J3C_CJUG_成果物一覧(2027.7)'!$A$1:$I$54</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +35,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -109,9 +109,9 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{19846205-E8F4-4FB7-B8FC-08971AABFEA7}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     &lt;プロンプト&gt;
 Ⅰ No / Zipファイル名 / 資料名
 👉 入力値そのまま（加工禁止）</t>
@@ -119,9 +119,9 @@
     </comment>
     <comment ref="D1" authorId="1" shapeId="0" xr:uid="{317EF476-0522-4885-A216-26B77EABBF19}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅱ 重要度
 &lt;プロンプト&gt;
 この資料がSDTM実務における意思決定や設計に与える影響度を、★〜★★★で評価せよ
@@ -141,9 +141,9 @@
     </comment>
     <comment ref="E1" authorId="2" shapeId="0" xr:uid="{C26FA529-675E-476C-A744-EFB84CE027D7}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅲ Key Word
 &lt;プロンプト&gt;
 本資料の論点構造を「実務的に意味のある単位」で5〜8個に分解し、
@@ -158,9 +158,9 @@
     </comment>
     <comment ref="F1" authorId="3" shapeId="0" xr:uid="{B1AA8D2B-817F-4553-8627-5730CFB32952}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅳ Summary（最重要）
 &lt;プロンプト&gt;
 本資料を「実務者が判断に使えるレベル」で詳細に要約せよ。
@@ -194,15 +194,15 @@
 ※長文可（むしろ推奨）
 ※ただしストーリー的文章ではなく、構造化して記載すること
 ※一般論・教科書的説明は禁止
-返信:
-【概要】だけを抽出</t>
+Reply:
+    【概要】だけを抽出</t>
       </text>
     </comment>
     <comment ref="G1" authorId="4" shapeId="0" xr:uid="{8E5DA6C1-0678-4A21-A0C4-306607E10DE4}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅴ 利用目的
 &lt;プロンプト&gt;
 本資料を「どの意思決定・設計判断の場面で使うか」を、
@@ -217,9 +217,9 @@
     </comment>
     <comment ref="H1" authorId="5" shapeId="0" xr:uid="{454E81C1-39D4-4CB4-806E-A016CC3F214B}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅵ 対象成果物 / ドメイン
 ■ プロンプト①（成果物）
 本資料が直接影響する成果物をCDISC成果物単位で列挙せよ
@@ -237,18 +237,22 @@
     </comment>
     <comment ref="I1" authorId="6" shapeId="0" xr:uid="{D2FAC706-4E56-495F-BE3A-4B726BA58C3C}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅶ 資料作成日
-年（YYYY）で統一する</t>
+年（YYYY）で統一する
+Reply:
+    細かいですが資料作成年にしておきました。
+Reply:
+    承知しました。ご確認ありがとうございました。</t>
       </text>
     </comment>
     <comment ref="J1" authorId="7" shapeId="0" xr:uid="{DA4421BD-C87D-47BB-B7FB-1F9491627A97}">
       <text>
-        <t xml:space="preserve">[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Ⅷ 実務分類
 本資料を以下のいずれかの分類に振り分けよ
 ①申請準備・規制当局対応（Form A/B, SDRG, PMDA等）
@@ -260,9 +264,9 @@
     </comment>
     <comment ref="D2" authorId="8" shapeId="0" xr:uid="{5E28E628-0263-444B-88D4-F790247C9387}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由（内部ロジック）
 知らなくてもSDTM設計・実装は可能
 判断・設計の選択にも影響しない
@@ -271,9 +275,9 @@
     </comment>
     <comment ref="D3" authorId="9" shapeId="0" xr:uid="{F79F4B5E-BC1D-4B6D-B442-FCFE4E58B5D6}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由（内部ロジック）
 実務判断（PPドメイン・言語運用）には影響する
 ただし従わなくてもSDTM自体は構築可能
@@ -282,9 +286,9 @@
     </comment>
     <comment ref="D4" authorId="10" shapeId="0" xr:uid="{B0F6D0FB-FB95-4976-B60B-BEBE32E4B1D9}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由（内部ロジック）
 翻訳依存は設計ミス要因になるが、従わなくてもSDTM構築自体は可能
 設計の「必須前提」ではなく「判断・注意事項」
@@ -293,9 +297,9 @@
     </comment>
     <comment ref="D5" authorId="11" shapeId="0" xr:uid="{3F1A39CB-0E5B-453A-B563-1F480BF64E88}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDTM設計・実装・判断に直接影響しない
 チーム運営・活動紹介が主目的
@@ -304,9 +308,9 @@
     </comment>
     <comment ref="D6" authorId="12" shapeId="0" xr:uid="{B323EEAD-999B-4E86-B9C2-584B4B5405FE}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Validationを「ツール依存」から「設計可能なルール」に変えるアプローチ
 P21未対応領域（APドメイン等）では代替手段がない
@@ -316,9 +320,9 @@
     </comment>
     <comment ref="D7" authorId="13" shapeId="0" xr:uid="{B335B4B3-BAE8-43D3-B5B5-6F8FEBB04661}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 STUDYID・DM・--DYなどSDTMコア設計の前提を規定
 誤るとValidationが成立しない／レビュー不可になる
@@ -328,9 +332,9 @@
     </comment>
     <comment ref="D8" authorId="14" shapeId="0" xr:uid="{4431AF24-481A-4DE8-AFD9-12BC8C7AF81D}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Rの活用事例・チーム活動紹介が主内容
 SDTM設計・Validation・規制対応には直接影響しない
@@ -339,9 +343,9 @@
     </comment>
     <comment ref="D9" authorId="15" shapeId="0" xr:uid="{1228F847-3F94-4360-8680-1126F3AAB912}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDTMIGで不足する領域の設計方針（どう拡張するか）を規定
 TAUGを使わないと、疾患特有データの格納方法が定義できない
@@ -351,9 +355,9 @@
     </comment>
     <comment ref="D10" authorId="16" shapeId="0" xr:uid="{577BD282-E4DF-46AE-825B-EBEAEF72AE76}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 CT・Dataset・Variableの統一ルール（企業横断）を規定
 統一しないとISS/ISE・提出データ統合が成立しない
@@ -363,9 +367,9 @@
     </comment>
     <comment ref="D11" authorId="17" shapeId="0" xr:uid="{76F4729B-F312-47F3-91B2-B021E3505088}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 チーム活動・プロトコル作成プロセスの紹介が主目的
 SDTM構造・Validation・提出設計には直接影響しない
@@ -374,9 +378,9 @@
     </comment>
     <comment ref="D12" authorId="18" shapeId="0" xr:uid="{3890DF69-85D0-4734-B056-1195EB622A6A}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 模擬試験におけるDV（Deviations）チームの活動報告
 SDTM設計・Validation・提出仕様に直接影響しない
@@ -385,9 +389,9 @@
     </comment>
     <comment ref="D13" authorId="19" shapeId="0" xr:uid="{84AF2E1D-AF1D-4E96-8E44-97AF345DC9EB}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 紙CRFチームの進捗報告・運用内容
 SDTM設計・Validation・提出仕様に直接影響しない
@@ -396,9 +400,9 @@
     </comment>
     <comment ref="D14" authorId="20" shapeId="0" xr:uid="{36608F8C-1A1A-4D31-9B59-D79E678B349B}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 TAUG（乳がん）の意訳作成およびチーム活動報告が主内容
 SDTM設計そのものの原則を規定しているわけではない
@@ -407,9 +411,9 @@
     </comment>
     <comment ref="D15" authorId="21" shapeId="0" xr:uid="{6D0263A8-0DA8-46FE-A776-C7FA28A668BA}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 TAUGの具体的実装例・詳細モデリングを提供
 設計判断（TU/TR/RS、NSV、RELREC）に強く影響する
@@ -419,9 +423,9 @@
     </comment>
     <comment ref="D16" authorId="22" shapeId="0" xr:uid="{EAFDF0BC-8FCF-4D8A-A164-3871CBD4C2D7}">
       <text>
-        <t xml:space="preserve">[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 腫瘍データ（TU/TR/RS）の具体実装ロジックを示す
 実装判断には強く影響するが
@@ -432,9 +436,9 @@
     </comment>
     <comment ref="D17" authorId="23" shapeId="0" xr:uid="{CFD7430B-37A4-448E-9640-9C2A0A4FFAC6}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Define.xml設計の中核（VLM設計方針）を扱う
 誤るとValidation通過・説明可能性が破綻
@@ -444,9 +448,9 @@
     </comment>
     <comment ref="D18" authorId="24" shapeId="0" xr:uid="{D312B4DD-C073-447F-A5E3-946BF1901547}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 模擬試験（PV0363）の全体活動・運用・進捗説明
 SDTM設計ルールや提出仕様の規定ではない
@@ -455,9 +459,9 @@
     </comment>
     <comment ref="D19" authorId="25" shapeId="0" xr:uid="{6BA08CFA-D594-4FD9-A9E3-EB0F9602216E}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 CJUG活動内のコミュニケーション施策（チャッティングセッション）の報告
 SDTM設計・提出・Validationには直接関係しない
@@ -466,9 +470,9 @@
     </comment>
     <comment ref="D20" authorId="26" shapeId="0" xr:uid="{A341EFA7-D688-4664-95FB-CA846F42A735}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 CJUG SDTMの年間活動報告（組織・活動・成果一覧）
 SDTM設計ルールや提出仕様ではない
@@ -477,9 +481,9 @@
     </comment>
     <comment ref="D21" authorId="27" shapeId="0" xr:uid="{0D0EDF0A-00FD-4846-ABA5-936EDA17457A}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 模擬試験（PV0363）の進捗共有・チーム運営・タスク整理の会議資料
 SDTM設計ルールではなくプロジェクト運営・実行フェーズの話
@@ -488,9 +492,9 @@
     </comment>
     <comment ref="D22" authorId="28" shapeId="0" xr:uid="{157065DE-8041-451A-AD6A-312A7F256E14}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Trial Design Dataset（TA/TE/TI/TS/TV）の実装・PGM設計・Validationを扱う
 実務（Spec作成・SAS・P21対応）に直結
@@ -500,9 +504,9 @@
     </comment>
     <comment ref="D23" authorId="29" shapeId="0" xr:uid="{B0C84467-6600-45CB-BB62-5BB6CE6A8F61}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDTMデータのRによる処理・分析・レポーティングを扱う
 実務効率（DM・Programming）の改善に直結
@@ -512,9 +516,9 @@
     </comment>
     <comment ref="D24" authorId="30" shapeId="0" xr:uid="{2DDBE955-71DF-4C09-8781-AA3E1A74912D}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Custom Domainの**実態（使用状況・体制・課題）**を把握できる
 実務判断（作るか・どう作るか）に影響
@@ -524,9 +528,9 @@
     </comment>
     <comment ref="D25" authorId="31" shapeId="0" xr:uid="{E294FFC4-9630-4B7C-8150-1593B8D66697}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 CT（Controlled Terminology）の全社管理戦略・運用設計を扱う
 SDTM/ADaM/統合解析すべてに影響する基盤レイヤー
@@ -536,9 +540,9 @@
     </comment>
     <comment ref="G25" authorId="32" shapeId="0" xr:uid="{1326E5A0-4F68-4B00-9736-42D9DA1BCF1E}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ✅ 補足（超重要）
 これは今回の中でトップクラスに重要です👇
 ✔ 本質
@@ -569,9 +573,9 @@
     </comment>
     <comment ref="D26" authorId="33" shapeId="0" xr:uid="{5C351452-919C-41B9-B77B-8D907D503036}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 FDA Validator / Business / Conformance Rulesの構造・差分・背景を整理
 P21 Validationの本質理解に直結
@@ -581,9 +585,9 @@
     </comment>
     <comment ref="D27" authorId="34" shapeId="0" xr:uid="{6C5464AC-D30F-4D00-AE0E-882F866722AC}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 DMドメインのRACE（人種）の定義・収集・CT・Validationを横断
 FDAガイダンス、CT仕様、P21 Validationの矛盾を扱う重要テーマ
@@ -593,9 +597,9 @@
     </comment>
     <comment ref="D28" authorId="35" shapeId="0" xr:uid="{46B7C18B-C40D-49AD-BF34-47F7822795F1}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDTM QCの**全体戦略（何を・いつ・どうやるか）**を体系化
 実務のボトルネック（リソース不足）に対する解決策を提示
@@ -605,9 +609,9 @@
     </comment>
     <comment ref="D29" authorId="36" shapeId="0" xr:uid="{6A6EB761-EBAC-4C70-9683-9729279340E3}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDTMをレビュー（中央モニタリング）に直接活用する実践例
 「提出用」から「業務活用」への転換を扱う
@@ -617,9 +621,9 @@
     </comment>
     <comment ref="D30" authorId="37" shapeId="0" xr:uid="{69854967-4249-430B-85CA-5D20140525A8}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDTM × AIの応用可能性探索
 実務への直接適用はまだ限定的
@@ -629,9 +633,9 @@
     </comment>
     <comment ref="D31" authorId="38" shapeId="0" xr:uid="{8A128531-DE79-4A96-86A4-F8672A0D1605}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Trial Design（TS/TI/TA）の実践的な修正・運用問題を詳細に扱う
 プロトコル変更・EPOCH整合・Validation限界など実務の本質問題を網羅
@@ -641,9 +645,9 @@
     </comment>
     <comment ref="D32" authorId="39" shapeId="0" xr:uid="{89D1D0C8-BF74-4C27-9636-BCE902850EF9}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 **Pinnacle21 Validationの“実運用”**をそのまま再現
 エラー原因（EDC / Mapping / Coding）を体系的に分解
@@ -653,9 +657,9 @@
     </comment>
     <comment ref="D33" authorId="40" shapeId="0" xr:uid="{DBF2F91A-4DE2-4D6E-9774-99C9D517E4A9}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 AE / MH / CM の実コード体系（MedDRA / ATC）を完全実装した実データ
 Coding運用（LLT→PT→SOC）をそのまま確認可能
@@ -665,9 +669,9 @@
     </comment>
     <comment ref="D34" authorId="41" shapeId="0" xr:uid="{B4E2108F-EBFB-4997-9CF6-2F6985BC1F4A}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDRG（提出文書）におけるIssue Summaryの実例
 Validation結果をどう説明するかという最終工程
@@ -677,9 +681,9 @@
     </comment>
     <comment ref="D35" authorId="42" shapeId="0" xr:uid="{4A1308D3-AEAF-4786-9FD0-B3D8D941BDB7}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 define.xml作成・バリデーション・クロスチェックの実務課題を網羅
 Datasetとの整合（XPT vs metadata）の問題を具体的に提示
@@ -689,9 +693,9 @@
     </comment>
     <comment ref="D36" authorId="43" shapeId="0" xr:uid="{425C0A4D-B815-4C69-84EA-E47196D2CE87}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 SDRGの全文構成・作成プロセス・実務判断を網羅
 （Issue Summary）の上位概念（SDRG全体）
@@ -701,9 +705,9 @@
     </comment>
     <comment ref="D37" authorId="44" shapeId="0" xr:uid="{DE5CC25E-1603-4502-910F-649ED0906595}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 実際のSDRG完成版（提出レベル）
 （Issue Summary）・（方針）の最終アウトプット
@@ -713,9 +717,9 @@
     </comment>
     <comment ref="D38" authorId="45" shapeId="0" xr:uid="{BD6952E2-1357-4B23-8CBD-5A40DD7FF826}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ★★★
 👉 判定理由
 プロジェクト全体（EDC～SDRGまで）を横断的に総括
@@ -726,9 +730,9 @@
     </comment>
     <comment ref="D39" authorId="46" shapeId="0" xr:uid="{832D64A1-E13D-4508-9EE3-4790663CF23E}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 中間解析という“非定常ケース”のSDTM設計を網羅
 PMDA提出前提の実務判断・設計方針を具体化
@@ -738,9 +742,9 @@
     </comment>
     <comment ref="D40" authorId="47" shapeId="0" xr:uid="{A30F537E-956D-4C90-B651-27EA6B3BBF21}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Legacy Data Conversion（LDC）という実務の難所を網羅
 SDTM変換の“前工程（レガシー移行）”のリアル課題
@@ -750,9 +754,9 @@
     </comment>
     <comment ref="D41" authorId="48" shapeId="0" xr:uid="{349A5CB3-E14F-4CE6-B596-E1E5848EC644}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 PMDA電子データ提出の必須ドキュメント（Form A/B）を体系化
 SDTM提出そのものではなく、規制とのインターフェースを扱う
@@ -762,9 +766,9 @@
     </comment>
     <comment ref="D42" authorId="49" shapeId="0" xr:uid="{D1830227-84B4-4936-A1DF-BCE59030F066}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 P21で検出できないSDTM問題を体系的に整理した唯一クラス資料
 実務で最も致命的な「すり抜けIssue」を網羅
@@ -774,9 +778,9 @@
     </comment>
     <comment ref="D43" authorId="50" shapeId="0" xr:uid="{6C991362-662A-4601-A5BA-94DCF4C19917}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 「LDC」をさらに実務寄りに具体化した超実践資料
 “他人が作ったデータ”という最悪ケースに対する標準手順
@@ -786,9 +790,9 @@
     </comment>
     <comment ref="D45" authorId="51" shapeId="0" xr:uid="{8680D9B1-08F2-4DC7-97EE-421291F5D309}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉 判定理由
 Form A/B（別紙8）の実運用・外部委託のリアルな実態
 056（LDC）や054（Form A）と直結
@@ -798,9 +802,9 @@
     </comment>
     <comment ref="D46" authorId="52" shapeId="0" xr:uid="{8A53866B-B780-446C-9133-E680C9425E7D}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉判定理由
 ・SDTM・ADaM作成の入出力・依存関係・工程設計が明示されている
 ・Define.xml／SDRG／Validationの位置づけを構造的に理解できる
@@ -810,9 +814,9 @@
     </comment>
     <comment ref="D47" authorId="53" shapeId="0" xr:uid="{6EBF33F3-DA93-47B6-8B58-006A35B13E16}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉判定理由
 ・Form A廃止後の説明責任をcSDRGに集約する前提を規定している
 ・Define.xml・SDRG・ADRG間の記載分担ルールを実務レベルで具体化している
@@ -822,9 +826,9 @@
     </comment>
     <comment ref="D48" authorId="54" shapeId="0" xr:uid="{E8773821-5EEC-451D-8E52-E1DF19DF39BB}">
       <text>
-        <t xml:space="preserve">[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     👉判定理由
 ・cSDRG Tips集の背景・意図・判断根拠を補足する資料
 ・Form A廃止後のcSDRG統合方針の考え方を明示
@@ -835,9 +839,9 @@
     </comment>
     <comment ref="D49" authorId="55" shapeId="0" xr:uid="{0AFE0795-A999-429F-99D2-96F8E7080B3F}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     判定理由
 ・cSDRG作成時の記載方針だけでなく、PMDA技術的ガイド、申請電子データ通知、FAQの要求事項を実務レベルへ落とし込んでいる。
 ・Define.xml、SDRG、ADRG、LDCPの責任分担と記載場所を具体的に規定している。
@@ -846,9 +850,9 @@
     </comment>
     <comment ref="D50" authorId="56" shapeId="0" xr:uid="{3EB1CAD2-39F3-4277-A80D-31D69B099A0D}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     判定理由
 ・cSDRG Tips集 Version2.0 の作成背景・検討方法・追加内容を説明する紹介資料である。 
 ・PMDA通知・技術的ガイド・FAQとcSDRGの関係を整理しており、実装判断の根拠を提供している。
@@ -857,9 +861,9 @@
     </comment>
     <comment ref="D51" authorId="57" shapeId="0" xr:uid="{11F94556-3C2C-4BB5-8414-218F42B016C1}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     判定理由
 ・FDA提出済パッケージをPMDA提出用へ変換する際の設計判断基準を提示している。 
 ・SDTM修正要否、RELREC対応、SI単位対応、SDTMIGバージョン差異対応、
@@ -869,17 +873,17 @@
     </comment>
     <comment ref="D52" authorId="58" shapeId="0" xr:uid="{51555F0F-4DB3-411A-97AC-3FC8A52D9A9B}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     「IG3.3で何が変わったか」ではなく、「IG3.3でSDTMをどう設計すべきか」を規定する資料であり、知らないとドメイン設計・Define.xml設計・Validation対応を誤る可能性があるため</t>
       </text>
     </comment>
     <comment ref="D53" authorId="59" shapeId="0" xr:uid="{28668CE2-7799-425F-AD52-D605620A5C99}">
       <text>
-        <t>[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ・cSDRGの記載内容そのものを規定する資料である。 
 ・PMDA・FDA審査時の説明責任に直接影響する。
 ・Validation Issue説明方法を規定している。
@@ -890,9 +894,9 @@
     </comment>
     <comment ref="D54" authorId="60" shapeId="0" xr:uid="{93C6BA0D-5270-41ED-A758-4250D0906C23}">
       <text>
-        <t xml:space="preserve">[スレッド化されたコメント]
-使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
-コメント:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Define-XML v2.1の設計ルールそのものを説明している。 
 def:Standards導入という構造変更を含む。 
 Origin定義の考え方が変わる。 
@@ -944,7 +948,11 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>資料作成日</t>
+    <t>資料作成年</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>実務分類</t>
@@ -2562,7 +2570,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2748,7 +2756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2824,6 +2832,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2852,6 +2866,8 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="masafumi kikura" id="{B943F829-6134-4124-955E-97F4C90B27D1}" userId="S::m-kikura@fujimoto-pharm.jp::01ce4d96-dd78-4d29-8836-2dd15da233d3" providerId="AD"/>
+  <person displayName="Minami, Kenta" id="{AF70188C-AE48-4F12-93B4-3C1E20C27349}" userId="S::kenta.minami@thermofisher.com::dc4e9742-94fa-4e46-859c-f3e1d48c617f" providerId="AD"/>
+  <person displayName="masafumi kikura" id="{ACE47DA0-522F-46F4-A8BB-31A5ABDCE327}" userId="S::m-kikura_fujimoto-pharm.jp#ext#@kmbiologics365.onmicrosoft.com::804ba3df-f9c4-4ab2-963c-633df81fe4e6" providerId="AD"/>
 </personList>
 </file>
 
@@ -3271,9 +3287,15 @@
 ・「全ドメイン」は禁止
 ・曖昧表現を使わない</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-06-29T04:09:19.72" personId="{B943F829-6134-4124-955E-97F4C90B27D1}" id="{D2FAC706-4E56-495F-BE3A-4B726BA58C3C}">
+  <threadedComment ref="I1" dT="2026-06-29T04:09:19.72" personId="{B943F829-6134-4124-955E-97F4C90B27D1}" id="{D2FAC706-4E56-495F-BE3A-4B726BA58C3C}" done="1">
     <text>Ⅶ 資料作成日
 年（YYYY）で統一する</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2026-08-03T02:17:00.78" personId="{AF70188C-AE48-4F12-93B4-3C1E20C27349}" id="{D990AADC-F0F6-4D21-B37C-C67153D470B1}" parentId="{D2FAC706-4E56-495F-BE3A-4B726BA58C3C}">
+    <text>細かいですが資料作成年にしておきました。</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2026-08-06T02:55:24.91" personId="{ACE47DA0-522F-46F4-A8BB-31A5ABDCE327}" id="{E3E27759-5424-40AE-BF73-E16FAEC641A0}" parentId="{D2FAC706-4E56-495F-BE3A-4B726BA58C3C}">
+    <text>承知しました。ご確認ありがとうございました。</text>
   </threadedComment>
   <threadedComment ref="J1" dT="2026-07-30T05:48:54.71" personId="{B943F829-6134-4124-955E-97F4C90B27D1}" id="{DA4421BD-C87D-47BB-B7FB-1F9491627A97}">
     <text xml:space="preserve">Ⅷ 実務分類
@@ -3667,8 +3689,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B1D3B59-B008-4903-95F0-3342D656A05A}">
-  <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K118"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="3" customWidth="1"/>
@@ -3681,7 +3703,7 @@
     <col min="10" max="10" width="9.625" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="19.149999999999999" thickTop="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3712,11 +3734,11 @@
       <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="8" customFormat="1" ht="48.75" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="48.6" thickTop="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3747,11 +3769,11 @@
       <c r="J2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -3782,11 +3804,11 @@
       <c r="J3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3817,11 +3839,11 @@
       <c r="J4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -3852,11 +3874,11 @@
       <c r="J5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="K5" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="8" customFormat="1" ht="96" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" s="8" customFormat="1" ht="96">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -3887,11 +3909,11 @@
       <c r="J6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="26" t="s">
+      <c r="K6" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -3922,11 +3944,11 @@
       <c r="J7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -3957,11 +3979,11 @@
       <c r="J8" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -3992,11 +4014,11 @@
       <c r="J9" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -4027,11 +4049,11 @@
       <c r="J10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -4062,11 +4084,11 @@
       <c r="J11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -4097,11 +4119,11 @@
       <c r="J12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -4130,11 +4152,11 @@
       <c r="J13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A14" s="19" t="s">
         <v>90</v>
       </c>
@@ -4163,11 +4185,11 @@
       <c r="J14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A15" s="9" t="s">
         <v>97</v>
       </c>
@@ -4198,11 +4220,11 @@
       <c r="J15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A16" s="9" t="s">
         <v>103</v>
       </c>
@@ -4233,11 +4255,11 @@
       <c r="J16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K16" s="26" t="s">
+      <c r="K16" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A17" s="9">
         <v>14</v>
       </c>
@@ -4268,11 +4290,11 @@
       <c r="J17" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A18" s="9">
         <v>15</v>
       </c>
@@ -4303,11 +4325,11 @@
       <c r="J18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="26" t="s">
+      <c r="K18" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A19" s="9">
         <v>16</v>
       </c>
@@ -4338,11 +4360,11 @@
       <c r="J19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="26" t="s">
+      <c r="K19" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A20" s="9">
         <v>17</v>
       </c>
@@ -4373,11 +4395,11 @@
       <c r="J20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="26" t="s">
+      <c r="K20" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A21" s="9">
         <v>18</v>
       </c>
@@ -4408,11 +4430,11 @@
       <c r="J21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="26" t="s">
+      <c r="K21" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A22" s="9">
         <v>19</v>
       </c>
@@ -4443,11 +4465,11 @@
       <c r="J22" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K22" s="26" t="s">
+      <c r="K22" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A23" s="9">
         <v>20</v>
       </c>
@@ -4478,11 +4500,11 @@
       <c r="J23" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K23" s="26" t="s">
+      <c r="K23" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A24" s="9">
         <v>21</v>
       </c>
@@ -4513,11 +4535,11 @@
       <c r="J24" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K24" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A25" s="9">
         <v>22</v>
       </c>
@@ -4548,11 +4570,11 @@
       <c r="J25" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" s="8" customFormat="1" ht="72">
       <c r="A26" s="18">
         <v>23</v>
       </c>
@@ -4583,11 +4605,11 @@
       <c r="J26" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A27" s="18">
         <v>24</v>
       </c>
@@ -4618,11 +4640,11 @@
       <c r="J27" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="K27" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A28" s="18">
         <v>25</v>
       </c>
@@ -4653,11 +4675,11 @@
       <c r="J28" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K28" s="26" t="s">
+      <c r="K28" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A29" s="18">
         <v>26</v>
       </c>
@@ -4688,11 +4710,11 @@
       <c r="J29" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K29" s="26" t="s">
+      <c r="K29" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A30" s="18">
         <v>27</v>
       </c>
@@ -4723,11 +4745,11 @@
       <c r="J30" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="26" t="s">
+      <c r="K30" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A31" s="18">
         <v>28</v>
       </c>
@@ -4758,11 +4780,11 @@
       <c r="J31" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K31" s="26" t="s">
+      <c r="K31" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A32" s="18" t="s">
         <v>196</v>
       </c>
@@ -4793,11 +4815,11 @@
       <c r="J32" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K32" s="26" t="s">
+      <c r="K32" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A33" s="18" t="s">
         <v>203</v>
       </c>
@@ -4828,11 +4850,11 @@
       <c r="J33" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="26" t="s">
+      <c r="K33" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A34" s="18" t="s">
         <v>208</v>
       </c>
@@ -4863,11 +4885,11 @@
       <c r="J34" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K34" s="26" t="s">
+      <c r="K34" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A35" s="18">
         <v>30</v>
       </c>
@@ -4898,11 +4920,11 @@
       <c r="J35" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K35" s="26" t="s">
+      <c r="K35" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A36" s="18" t="s">
         <v>220</v>
       </c>
@@ -4933,11 +4955,11 @@
       <c r="J36" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K36" s="26" t="s">
+      <c r="K36" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A37" s="18" t="s">
         <v>227</v>
       </c>
@@ -4968,11 +4990,11 @@
       <c r="J37" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K37" s="26" t="s">
+      <c r="K37" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="8" customFormat="1" ht="36" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" s="8" customFormat="1" ht="36">
       <c r="A38" s="18">
         <v>32</v>
       </c>
@@ -5003,11 +5025,11 @@
       <c r="J38" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K38" s="26" t="s">
+      <c r="K38" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" s="8" customFormat="1" ht="60">
       <c r="A39" s="18">
         <v>33</v>
       </c>
@@ -5038,11 +5060,11 @@
       <c r="J39" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K39" s="26" t="s">
+      <c r="K39" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A40" s="18">
         <v>34</v>
       </c>
@@ -5073,11 +5095,11 @@
       <c r="J40" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K40" s="26" t="s">
+      <c r="K40" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A41" s="18">
         <v>35</v>
       </c>
@@ -5108,11 +5130,11 @@
       <c r="J41" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K41" s="26" t="s">
+      <c r="K41" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A42" s="18">
         <v>36</v>
       </c>
@@ -5143,11 +5165,11 @@
       <c r="J42" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K42" s="26" t="s">
+      <c r="K42" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A43" s="18" t="s">
         <v>261</v>
       </c>
@@ -5178,11 +5200,11 @@
       <c r="J43" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K43" s="26" t="s">
+      <c r="K43" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" s="8" customFormat="1" ht="48">
       <c r="A44" s="18" t="s">
         <v>268</v>
       </c>
@@ -5213,11 +5235,11 @@
       <c r="J44" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K44" s="26" t="s">
+      <c r="K44" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="8" customFormat="1" ht="108" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" s="8" customFormat="1" ht="108">
       <c r="A45" s="20">
         <v>38</v>
       </c>
@@ -5248,11 +5270,11 @@
       <c r="J45" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K45" s="26" t="s">
+      <c r="K45" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="8" customFormat="1" ht="156" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" s="8" customFormat="1" ht="156">
       <c r="A46" s="20">
         <v>39</v>
       </c>
@@ -5283,11 +5305,11 @@
       <c r="J46" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K46" s="26" t="s">
+      <c r="K46" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A47" s="20" t="s">
         <v>287</v>
       </c>
@@ -5318,11 +5340,11 @@
       <c r="J47" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K47" s="26" t="s">
+      <c r="K47" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="8" customFormat="1" ht="96" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" s="8" customFormat="1" ht="96">
       <c r="A48" s="20" t="s">
         <v>294</v>
       </c>
@@ -5353,11 +5375,11 @@
       <c r="J48" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K48" s="26" t="s">
+      <c r="K48" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A49" s="20" t="s">
         <v>300</v>
       </c>
@@ -5388,11 +5410,11 @@
       <c r="J49" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="K49" s="26" t="s">
+      <c r="K49" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A50" s="20" t="s">
         <v>307</v>
       </c>
@@ -5423,11 +5445,11 @@
       <c r="J50" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="K50" s="26" t="s">
+      <c r="K50" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="8" customFormat="1" ht="120" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" s="8" customFormat="1" ht="120">
       <c r="A51" s="20">
         <v>42</v>
       </c>
@@ -5458,11 +5480,11 @@
       <c r="J51" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="K51" s="26" t="s">
+      <c r="K51" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="8" customFormat="1" ht="192" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" s="8" customFormat="1" ht="192">
       <c r="A52" s="18">
         <v>42</v>
       </c>
@@ -5493,11 +5515,11 @@
       <c r="J52" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="K52" s="26" t="s">
+      <c r="K52" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="8" customFormat="1" ht="168" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" s="8" customFormat="1" ht="168">
       <c r="A53" s="18">
         <v>43</v>
       </c>
@@ -5528,11 +5550,11 @@
       <c r="J53" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="K53" s="26" t="s">
+      <c r="K53" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="8" customFormat="1" ht="156" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" s="8" customFormat="1" ht="156">
       <c r="A54" s="18">
         <v>44</v>
       </c>
@@ -5563,9 +5585,841 @@
       <c r="J54" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="K54" s="26" t="s">
+      <c r="K54" s="28" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="55" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A55" s="18"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="26"/>
+    </row>
+    <row r="56" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A56" s="18"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="26"/>
+    </row>
+    <row r="57" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A57" s="18"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="26"/>
+    </row>
+    <row r="58" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A58" s="18"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="26"/>
+    </row>
+    <row r="59" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A59" s="18"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="26"/>
+    </row>
+    <row r="60" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A60" s="18"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="26"/>
+    </row>
+    <row r="61" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A61" s="18"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="26"/>
+    </row>
+    <row r="62" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A62" s="9"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="26"/>
+    </row>
+    <row r="63" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A63" s="9"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="26"/>
+    </row>
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A64" s="9"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A65" s="9"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="26"/>
+    </row>
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A66" s="9"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="26"/>
+    </row>
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A67" s="9"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="26"/>
+    </row>
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A68" s="9"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="26"/>
+    </row>
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A69" s="9"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="26"/>
+    </row>
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A70" s="9"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="26"/>
+    </row>
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A71" s="9"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="26"/>
+    </row>
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A72" s="9"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="26"/>
+    </row>
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A73" s="9"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="26"/>
+    </row>
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A74" s="9"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="26"/>
+    </row>
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A75" s="9"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="26"/>
+    </row>
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A76" s="9"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="26"/>
+    </row>
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A77" s="9"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="26"/>
+    </row>
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A78" s="9"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="26"/>
+    </row>
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A79" s="9"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="26"/>
+    </row>
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A80" s="9"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="26"/>
+    </row>
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A81" s="9"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="26"/>
+    </row>
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A82" s="9"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="26"/>
+    </row>
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A83" s="9"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="26"/>
+    </row>
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A84" s="9"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="26"/>
+    </row>
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A85" s="9"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="26"/>
+    </row>
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A86" s="9"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="26"/>
+    </row>
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A87" s="9"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="26"/>
+    </row>
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A88" s="9"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="25"/>
+      <c r="K88" s="26"/>
+    </row>
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A89" s="9"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="26"/>
+    </row>
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A90" s="9"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
+      <c r="H90" s="16"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="25"/>
+      <c r="K90" s="26"/>
+    </row>
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A91" s="9"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="25"/>
+      <c r="K91" s="26"/>
+    </row>
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A92" s="9"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="25"/>
+      <c r="K92" s="26"/>
+    </row>
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A93" s="9"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="25"/>
+      <c r="K93" s="26"/>
+    </row>
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A94" s="9"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="25"/>
+      <c r="K94" s="26"/>
+    </row>
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A95" s="9"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="25"/>
+      <c r="K95" s="26"/>
+    </row>
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A96" s="9"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="16"/>
+      <c r="H96" s="16"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="25"/>
+      <c r="K96" s="26"/>
+    </row>
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A97" s="9"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="25"/>
+      <c r="K97" s="26"/>
+    </row>
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A98" s="9"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="16"/>
+      <c r="H98" s="16"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="25"/>
+      <c r="K98" s="26"/>
+    </row>
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A99" s="9"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="16"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="25"/>
+      <c r="K99" s="26"/>
+    </row>
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A100" s="9"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="25"/>
+      <c r="K100" s="26"/>
+    </row>
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A101" s="9"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="25"/>
+      <c r="K101" s="26"/>
+    </row>
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A102" s="9"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="25"/>
+      <c r="K102" s="26"/>
+    </row>
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A103" s="9"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="25"/>
+      <c r="K103" s="26"/>
+    </row>
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A104" s="9"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="25"/>
+      <c r="K104" s="26"/>
+    </row>
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A105" s="9"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="16"/>
+      <c r="H105" s="16"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="25"/>
+      <c r="K105" s="26"/>
+    </row>
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A106" s="9"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="25"/>
+      <c r="K106" s="26"/>
+    </row>
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A107" s="9"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="16"/>
+      <c r="H107" s="16"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="25"/>
+      <c r="K107" s="26"/>
+    </row>
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A108" s="9"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="16"/>
+      <c r="H108" s="16"/>
+      <c r="I108" s="11"/>
+      <c r="J108" s="25"/>
+      <c r="K108" s="26"/>
+    </row>
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A109" s="9"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="11"/>
+      <c r="J109" s="25"/>
+      <c r="K109" s="26"/>
+    </row>
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A110" s="9"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="25"/>
+      <c r="K110" s="26"/>
+    </row>
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A111" s="9"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="25"/>
+      <c r="K111" s="26"/>
+    </row>
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A112" s="9"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="25"/>
+      <c r="K112" s="26"/>
+    </row>
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A113" s="9"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="11"/>
+      <c r="J113" s="25"/>
+      <c r="K113" s="26"/>
+    </row>
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A114" s="9"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
+      <c r="H114" s="16"/>
+      <c r="I114" s="11"/>
+      <c r="J114" s="25"/>
+      <c r="K114" s="26"/>
+    </row>
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A115" s="9"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="25"/>
+      <c r="K115" s="26"/>
+    </row>
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A116" s="9"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="16"/>
+      <c r="H116" s="16"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="25"/>
+      <c r="K116" s="26"/>
+    </row>
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A117" s="9"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="16"/>
+      <c r="H117" s="16"/>
+      <c r="I117" s="11"/>
+      <c r="J117" s="25"/>
+      <c r="K117" s="26"/>
+    </row>
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="16.149999999999999">
+      <c r="A118" s="9"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="16"/>
+      <c r="G118" s="16"/>
+      <c r="H118" s="16"/>
+      <c r="I118" s="11"/>
+      <c r="J118" s="25"/>
+      <c r="K118" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -5640,15 +6494,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100D9E08D8B46F3F64C965B15305CD1000D" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="128d2fce5b967bdcffde0ed16ad6e21b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f77ab5d5-5567-4c43-8a04-41d54c287387" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f51ae7fd5b2767200f42eaa72a05ab04" ns2:_="">
     <xsd:import namespace="f77ab5d5-5567-4c43-8a04-41d54c287387"/>
@@ -5832,44 +6677,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6B9A550-D6AE-4CCD-96E6-44574B50CD7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f77ab5d5-5567-4c43-8a04-41d54c287387"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6B9A550-D6AE-4CCD-96E6-44574B50CD7D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D7D843E-97EF-413D-824F-472B7A250457}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7E3CFA5-F8BD-4D96-9CE8-C5222E783B00}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7E3CFA5-F8BD-4D96-9CE8-C5222E783B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f77ab5d5-5567-4c43-8a04-41d54c287387"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D7D843E-97EF-413D-824F-472B7A250457}"/>
 </file>